--- a/data/externalStats/File1/RPT_RPT4636734643070GR_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT4636734643070GR_externalStats.xlsx
@@ -2181,7 +2181,7 @@
         <v>11053681.77593989</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>14824.51869790835</v>
+        <v>14824.51869790836</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>2681546.565749676</v>
+        <v>2681546.565749675</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>0</v>
@@ -3905,13 +3905,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.0648471281</v>
+        <v>6320.064847128099</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.407495872959</v>
+        <v>3125.407495872958</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7877512450654</v>
+        <v>790.7877512450652</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -3920,28 +3920,28 @@
         <v>10236.26009424612</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.830358097972</v>
+        <v>6124.830358097973</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>3021.838043207604</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.91190356957</v>
+        <v>757.9119035695702</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>9904.580304875144</v>
+        <v>9904.580304875146</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.504189498098</v>
+        <v>5957.504189498099</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>2933.086637895056</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.230904643476</v>
+        <v>729.2309046434758</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -3961,7 +3961,7 @@
         <v>3484095.766991229</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>4942.766476981106</v>
+        <v>4942.766476981107</v>
       </c>
     </row>
     <row r="54">
@@ -3986,13 +3986,13 @@
         <v>21126</v>
       </c>
       <c r="J54" s="130" t="n">
-        <v>14501.73838215771</v>
+        <v>14501.7383821577</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.46940470681</v>
+        <v>7845.469404706811</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>2325.731440101695</v>
+        <v>2325.731440101696</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>891.9942898548878</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.639414952088</v>
+        <v>890.6394149520879</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
@@ -4103,7 +4103,7 @@
         <v>887.5202998056624</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -4235,31 +4235,31 @@
         <v>1207.199009799243</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>447.1561923110474</v>
+        <v>447.1561923110473</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8263.713017195194</v>
+        <v>8263.713017195192</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6533.070130571056</v>
+        <v>6533.070130571055</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1132.596079860724</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>428.0039475295338</v>
+        <v>428.0039475295337</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8093.670157961314</v>
+        <v>8093.670157961312</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6654.18468522172</v>
+        <v>6654.184685221721</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1147.293027687765</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>995535.0231208121</v>
+        <v>995535.0231208123</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>0</v>
@@ -4715,34 +4715,34 @@
         <v>22805</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5637.393210158669</v>
+        <v>5637.393210158662</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1656.135414675062</v>
+        <v>1656.135414675058</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>607.4898571432227</v>
+        <v>607.4898571432223</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>22204.72312108167</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>30105.74160305862</v>
+        <v>30105.74160305861</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5875.167457966767</v>
+        <v>5875.167457966774</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1703.952920346313</v>
+        <v>1703.952920346315</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>629.784487875077</v>
+        <v>629.7844878750766</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>24494.24733707641</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32703.15220326457</v>
+        <v>32703.15220326458</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>6144.224276925168</v>
@@ -5126,7 +5126,7 @@
         <v>109542</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>53083.94013616577</v>
+        <v>53083.94013616576</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>14726.20561490896</v>
@@ -5162,7 +5162,7 @@
         <v>15913.04608529102</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>5035.70598772958</v>
+        <v>5035.705987729579</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>27126.77466866459</v>
@@ -5182,7 +5182,7 @@
         <v>299886.3791689929</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>927.3717440000001</v>
+        <v>927.371744</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -5336,22 +5336,22 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6291.051318998416</v>
+        <v>6291.051318998417</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1107.88301454501</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.0213856721393</v>
+        <v>357.0213856721392</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7755.955719215565</v>
+        <v>7755.955719215566</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6402.126106675359</v>
+        <v>6402.126106675362</v>
       </c>
       <c r="Q71" s="128" t="n">
         <v>1140.833474495618</v>
@@ -5363,22 +5363,22 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7908.851282991038</v>
+        <v>7908.851282991041</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6480.947150169953</v>
+        <v>6480.947150169954</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.110724660194</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>373.1823864536181</v>
+        <v>373.1823864536182</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8025.240261283765</v>
+        <v>8025.240261283766</v>
       </c>
     </row>
     <row r="72">
@@ -5418,7 +5418,7 @@
         <v>4.06795957729254</v>
       </c>
       <c r="P72" s="130" t="n">
-        <v>3.034850177968129</v>
+        <v>3.034850177968131</v>
       </c>
       <c r="Q72" s="131" t="n">
         <v>0.99935879958163</v>
@@ -5430,13 +5430,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="132" t="n">
-        <v>4.034208977549759</v>
+        <v>4.034208977549761</v>
       </c>
       <c r="V72" s="130" t="n">
         <v>3.004310589767974</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891315731220903</v>
+        <v>0.9891315731220905</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -5604,10 +5604,10 @@
         <v>428</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7725.40912219813</v>
+        <v>7725.409122198131</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2374.418161174764</v>
+        <v>2374.418161174763</v>
       </c>
       <c r="L75" s="131" t="n">
         <v>535.5877718652724</v>
@@ -5619,34 +5619,34 @@
         <v>10635.41505523817</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8643.557255466281</v>
+        <v>8643.557255466285</v>
       </c>
       <c r="Q75" s="131" t="n">
         <v>2736.307259689338</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>615.2216261623436</v>
+        <v>615.2216261623435</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T75" s="132" t="n">
-        <v>11995.08614131796</v>
+        <v>11995.08614131797</v>
       </c>
       <c r="V75" s="130" t="n">
         <v>9438.884141585029</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3047.279734764492</v>
+        <v>3047.279734764493</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>680.2887679058531</v>
+        <v>680.2887679058533</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z75" s="132" t="n">
-        <v>13166.45264425537</v>
+        <v>13166.45264425538</v>
       </c>
     </row>
     <row r="76">
@@ -6006,49 +6006,49 @@
         <v>2509</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="L81" s="131" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M81" s="131" t="n">
         <v>2908.033523731806</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2908.033523731808</v>
+        <v>2908.033523731807</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>-3.637978807091713e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="S81" s="131" t="n">
         <v>3233.974567580811</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>3233.974567580811</v>
+        <v>3233.974567580808</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>3567.196203083912</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>3567.196203083913</v>
+        <v>3567.19620308391</v>
       </c>
     </row>
     <row r="82">
@@ -6351,7 +6351,7 @@
         <v>3507.389747664738</v>
       </c>
       <c r="L86" s="143" t="n">
-        <v>892.609157537412</v>
+        <v>892.6091575374119</v>
       </c>
       <c r="M86" s="143" t="n">
         <v>2908.033523731806</v>
@@ -6544,10 +6544,10 @@
         <v>12611.11616612652</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>4233.290510417969</v>
+        <v>4233.290510417968</v>
       </c>
       <c r="L89" s="128" t="n">
-        <v>1147.809136917205</v>
+        <v>1147.809136917204</v>
       </c>
       <c r="M89" s="128" t="n">
         <v>0</v>
@@ -6556,7 +6556,7 @@
         <v>17992.21581346169</v>
       </c>
       <c r="P89" s="127" t="n">
-        <v>12526.95646477333</v>
+        <v>12526.95646477334</v>
       </c>
       <c r="Q89" s="128" t="n">
         <v>4162.671517703222</v>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>17813.43158786618</v>
+        <v>17813.43158786619</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>12438.45133966805</v>
@@ -6608,19 +6608,19 @@
         <v>21130</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>14504.79819544821</v>
+        <v>14504.7981954482</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.477550993601</v>
+        <v>7846.477550993602</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>2325.731440101695</v>
+        <v>2325.731440101696</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>24677.00718654351</v>
+        <v>24677.0071865435</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>15891.30418643938</v>
@@ -6635,7 +6635,7 @@
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>27000.84940712616</v>
+        <v>27000.84940712615</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>17731.73815568648</v>
@@ -6681,7 +6681,7 @@
         <v>891.9942898548878</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
@@ -6693,10 +6693,10 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.639414952088</v>
+        <v>890.6394149520879</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
@@ -6711,7 +6711,7 @@
         <v>887.5202998056624</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -6815,7 +6815,7 @@
         <v>3581.617170974006</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>982.7439641763199</v>
+        <v>982.7439641763198</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -7214,7 +7214,7 @@
         <v>5637.393210158669</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1656.13541467506</v>
+        <v>1656.135414675056</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>607.4898571432232</v>
@@ -7241,19 +7241,19 @@
         <v>35937.12677084539</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>6144.224276925175</v>
+        <v>6144.224276925161</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1767.142052340063</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>655.1214664631962</v>
+        <v>655.1214664631952</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>30693.9708717485</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>39260.45866747694</v>
+        <v>39260.45866747692</v>
       </c>
     </row>
     <row r="100">
@@ -7553,7 +7553,7 @@
         <v>67280.10770430029</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>18233.5953625737</v>
+        <v>18233.59536257369</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>5121.900829719571</v>
@@ -7580,13 +7580,13 @@
         <v>149710.839179817</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>72515.58812458278</v>
+        <v>72515.58812458276</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>20155.89452033806</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>6089.177142089051</v>
+        <v>6089.17714208905</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>30693.9708717485</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>1625494.155551699</v>
+        <v>1625494.1555517</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>1968.716811057299</v>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>874699.7081056555</v>
+        <v>874699.7081056554</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>41.20832881760001</v>
@@ -10429,13 +10429,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.0648471281</v>
+        <v>6320.064847128099</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.407495872959</v>
+        <v>3125.407495872958</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7877512450654</v>
+        <v>790.7877512450652</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -10444,28 +10444,28 @@
         <v>10236.26009424612</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.830358097972</v>
+        <v>6124.830358097973</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>3021.838043207604</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.91190356957</v>
+        <v>757.9119035695702</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>9904.580304875144</v>
+        <v>9904.580304875146</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.504189498098</v>
+        <v>5957.504189498099</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>2933.086637895056</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.230904643476</v>
+        <v>729.2309046434758</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -10510,13 +10510,13 @@
         <v>21126</v>
       </c>
       <c r="J54" s="130" t="n">
-        <v>14501.73838215771</v>
+        <v>14501.7383821577</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.46940470681</v>
+        <v>7845.469404706811</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>2325.731440101695</v>
+        <v>2325.731440101696</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>2350186.045036119</v>
+        <v>2350186.045036118</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>589.6962984580065</v>
@@ -10597,7 +10597,7 @@
         <v>891.9942898548878</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
@@ -10609,10 +10609,10 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.639414952088</v>
+        <v>890.6394149520879</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
@@ -10627,7 +10627,7 @@
         <v>887.5202998056624</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>1945845.153215984</v>
+        <v>1945845.153215983</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>0</v>
@@ -10759,31 +10759,31 @@
         <v>1207.199009799243</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>447.1561923110474</v>
+        <v>447.1561923110473</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8263.713017195194</v>
+        <v>8263.713017195192</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6533.070130571056</v>
+        <v>6533.070130571055</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1132.596079860724</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>428.0039475295338</v>
+        <v>428.0039475295337</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8093.670157961314</v>
+        <v>8093.670157961312</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6654.18468522172</v>
+        <v>6654.184685221721</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1147.293027687765</v>
@@ -11239,34 +11239,34 @@
         <v>22805</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5637.393210158669</v>
+        <v>5637.393210158662</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1656.135414675062</v>
+        <v>1656.135414675058</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>607.4898571432227</v>
+        <v>607.4898571432223</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>22204.72312108167</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>30105.74160305862</v>
+        <v>30105.74160305861</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5875.167457966767</v>
+        <v>5875.167457966774</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1703.952920346313</v>
+        <v>1703.952920346315</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>629.784487875077</v>
+        <v>629.7844878750766</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>24494.24733707641</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32703.15220326457</v>
+        <v>32703.15220326458</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>6144.224276925168</v>
@@ -11650,7 +11650,7 @@
         <v>109542</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>53083.94013616577</v>
+        <v>53083.94013616576</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>14726.20561490896</v>
@@ -11686,7 +11686,7 @@
         <v>15913.04608529102</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>5035.70598772958</v>
+        <v>5035.705987729579</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>27126.77466866459</v>
@@ -11706,7 +11706,7 @@
         <v>308238.7914176058</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>924.7472819644801</v>
+        <v>924.74728196448</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -11860,22 +11860,22 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6291.051318998416</v>
+        <v>6291.051318998417</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1107.88301454501</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.0213856721393</v>
+        <v>357.0213856721392</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7755.955719215565</v>
+        <v>7755.955719215566</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6402.126106675359</v>
+        <v>6402.126106675362</v>
       </c>
       <c r="Q71" s="128" t="n">
         <v>1140.833474495618</v>
@@ -11887,22 +11887,22 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7908.851282991038</v>
+        <v>7908.851282991041</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6480.947150169953</v>
+        <v>6480.947150169954</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.110724660194</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>373.1823864536181</v>
+        <v>373.1823864536182</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8025.240261283765</v>
+        <v>8025.240261283766</v>
       </c>
     </row>
     <row r="72">
@@ -11942,7 +11942,7 @@
         <v>4.06795957729254</v>
       </c>
       <c r="P72" s="130" t="n">
-        <v>3.034850177968129</v>
+        <v>3.034850177968131</v>
       </c>
       <c r="Q72" s="131" t="n">
         <v>0.99935879958163</v>
@@ -11954,13 +11954,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="132" t="n">
-        <v>4.034208977549759</v>
+        <v>4.034208977549761</v>
       </c>
       <c r="V72" s="130" t="n">
         <v>3.004310589767974</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891315731220903</v>
+        <v>0.9891315731220905</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>428</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7725.40912219813</v>
+        <v>7725.409122198131</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2374.418161174764</v>
+        <v>2374.418161174763</v>
       </c>
       <c r="L75" s="131" t="n">
         <v>535.5877718652724</v>
@@ -12143,34 +12143,34 @@
         <v>10635.41505523817</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8643.557255466281</v>
+        <v>8643.557255466285</v>
       </c>
       <c r="Q75" s="131" t="n">
         <v>2736.307259689338</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>615.2216261623436</v>
+        <v>615.2216261623435</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T75" s="132" t="n">
-        <v>11995.08614131796</v>
+        <v>11995.08614131797</v>
       </c>
       <c r="V75" s="130" t="n">
         <v>9438.884141585029</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3047.279734764492</v>
+        <v>3047.279734764493</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>680.2887679058531</v>
+        <v>680.2887679058533</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z75" s="132" t="n">
-        <v>13166.45264425537</v>
+        <v>13166.45264425538</v>
       </c>
     </row>
     <row r="76">
@@ -12530,49 +12530,49 @@
         <v>2509</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="L81" s="131" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M81" s="131" t="n">
         <v>2908.033523731806</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2908.033523731808</v>
+        <v>2908.033523731807</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>-3.637978807091713e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="S81" s="131" t="n">
         <v>3233.974567580811</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>3233.974567580811</v>
+        <v>3233.974567580808</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>3567.196203083912</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>3567.196203083913</v>
+        <v>3567.19620308391</v>
       </c>
     </row>
     <row r="82">
@@ -12875,7 +12875,7 @@
         <v>3507.389747664738</v>
       </c>
       <c r="L86" s="143" t="n">
-        <v>892.609157537412</v>
+        <v>892.6091575374119</v>
       </c>
       <c r="M86" s="143" t="n">
         <v>2908.033523731806</v>
@@ -13068,10 +13068,10 @@
         <v>12611.11616612652</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>4233.290510417969</v>
+        <v>4233.290510417968</v>
       </c>
       <c r="L89" s="128" t="n">
-        <v>1147.809136917205</v>
+        <v>1147.809136917204</v>
       </c>
       <c r="M89" s="128" t="n">
         <v>0</v>
@@ -13080,7 +13080,7 @@
         <v>17992.21581346169</v>
       </c>
       <c r="P89" s="127" t="n">
-        <v>12526.95646477333</v>
+        <v>12526.95646477334</v>
       </c>
       <c r="Q89" s="128" t="n">
         <v>4162.671517703222</v>
@@ -13092,7 +13092,7 @@
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>17813.43158786618</v>
+        <v>17813.43158786619</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>12438.45133966805</v>
@@ -13132,19 +13132,19 @@
         <v>21130</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>14504.79819544821</v>
+        <v>14504.7981954482</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.477550993601</v>
+        <v>7846.477550993602</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>2325.731440101695</v>
+        <v>2325.731440101696</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>24677.00718654351</v>
+        <v>24677.0071865435</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>15891.30418643938</v>
@@ -13159,7 +13159,7 @@
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>27000.84940712616</v>
+        <v>27000.84940712615</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>17731.73815568648</v>
@@ -13205,7 +13205,7 @@
         <v>891.9942898548878</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
@@ -13217,10 +13217,10 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.639414952088</v>
+        <v>890.6394149520879</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
@@ -13235,7 +13235,7 @@
         <v>887.5202998056624</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -13339,7 +13339,7 @@
         <v>3581.617170974006</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>982.7439641763199</v>
+        <v>982.7439641763198</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>5637.393210158669</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1656.13541467506</v>
+        <v>1656.135414675056</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>607.4898571432232</v>
@@ -13765,19 +13765,19 @@
         <v>35937.12677084539</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>6144.224276925175</v>
+        <v>6144.224276925161</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1767.142052340063</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>655.1214664631962</v>
+        <v>655.1214664631952</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>30693.9708717485</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>39260.45866747694</v>
+        <v>39260.45866747692</v>
       </c>
     </row>
     <row r="100">
@@ -14077,7 +14077,7 @@
         <v>67280.10770430029</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>18233.5953625737</v>
+        <v>18233.59536257369</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>5121.900829719571</v>
@@ -14104,13 +14104,13 @@
         <v>149710.839179817</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>72515.58812458278</v>
+        <v>72515.58812458276</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>20155.89452033806</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>6089.177142089051</v>
+        <v>6089.17714208905</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>30693.9708717485</v>
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>5844619.076846569</v>
+        <v>5844619.07684657</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>0</v>
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>1881079.821863848</v>
+        <v>1881079.821863847</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>2122.197973647326</v>
@@ -16414,7 +16414,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>884256.2432951636</v>
+        <v>884256.2432951637</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>1826.21205728125</v>
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>866828.4223870744</v>
+        <v>866828.4223870742</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>828.6349090366574</v>
@@ -16953,13 +16953,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.0648471281</v>
+        <v>6320.064847128099</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.407495872959</v>
+        <v>3125.407495872958</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7877512450654</v>
+        <v>790.7877512450652</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -16968,28 +16968,28 @@
         <v>10236.26009424612</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.830358097972</v>
+        <v>6124.830358097973</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>3021.838043207604</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.91190356957</v>
+        <v>757.9119035695702</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>9904.580304875144</v>
+        <v>9904.580304875146</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.504189498098</v>
+        <v>5957.504189498099</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>2933.086637895056</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.230904643476</v>
+        <v>729.2309046434758</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -17034,13 +17034,13 @@
         <v>21126</v>
       </c>
       <c r="J54" s="130" t="n">
-        <v>14501.73838215771</v>
+        <v>14501.7383821577</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.46940470681</v>
+        <v>7845.469404706811</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>2325.731440101695</v>
+        <v>2325.731440101696</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
@@ -17121,7 +17121,7 @@
         <v>891.9942898548878</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
@@ -17133,10 +17133,10 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.639414952088</v>
+        <v>890.6394149520879</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
@@ -17151,7 +17151,7 @@
         <v>887.5202998056624</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -17283,31 +17283,31 @@
         <v>1207.199009799243</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>447.1561923110474</v>
+        <v>447.1561923110473</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8263.713017195194</v>
+        <v>8263.713017195192</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6533.070130571056</v>
+        <v>6533.070130571055</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1132.596079860724</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>428.0039475295338</v>
+        <v>428.0039475295337</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8093.670157961314</v>
+        <v>8093.670157961312</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6654.18468522172</v>
+        <v>6654.184685221721</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1147.293027687765</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>884256.2432951637</v>
+        <v>884256.2432951636</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>2371.245811243431</v>
@@ -17492,7 +17492,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>830147.9715411521</v>
+        <v>830147.971541152</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>527.7572744857026</v>
@@ -17763,34 +17763,34 @@
         <v>22805</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5637.393210158669</v>
+        <v>5637.393210158662</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1656.135414675062</v>
+        <v>1656.135414675058</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>607.4898571432227</v>
+        <v>607.4898571432223</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>22204.72312108167</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>30105.74160305862</v>
+        <v>30105.74160305861</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5875.167457966767</v>
+        <v>5875.167457966774</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1703.952920346313</v>
+        <v>1703.952920346315</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>629.784487875077</v>
+        <v>629.7844878750766</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>24494.24733707641</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32703.15220326457</v>
+        <v>32703.15220326458</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>6144.224276925168</v>
@@ -18149,7 +18149,7 @@
         <v>320953.9661106729</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>920.2992475382309</v>
+        <v>920.2992475382308</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -18174,7 +18174,7 @@
         <v>109542</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>53083.94013616577</v>
+        <v>53083.94013616576</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>14726.20561490896</v>
@@ -18210,7 +18210,7 @@
         <v>15913.04608529102</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>5035.70598772958</v>
+        <v>5035.705987729579</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>27126.77466866459</v>
@@ -18384,22 +18384,22 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6291.051318998416</v>
+        <v>6291.051318998417</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1107.88301454501</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.0213856721393</v>
+        <v>357.0213856721392</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7755.955719215565</v>
+        <v>7755.955719215566</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6402.126106675359</v>
+        <v>6402.126106675362</v>
       </c>
       <c r="Q71" s="128" t="n">
         <v>1140.833474495618</v>
@@ -18411,22 +18411,22 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7908.851282991038</v>
+        <v>7908.851282991041</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6480.947150169953</v>
+        <v>6480.947150169954</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.110724660194</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>373.1823864536181</v>
+        <v>373.1823864536182</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8025.240261283765</v>
+        <v>8025.240261283766</v>
       </c>
     </row>
     <row r="72">
@@ -18466,7 +18466,7 @@
         <v>4.06795957729254</v>
       </c>
       <c r="P72" s="130" t="n">
-        <v>3.034850177968129</v>
+        <v>3.034850177968131</v>
       </c>
       <c r="Q72" s="131" t="n">
         <v>0.99935879958163</v>
@@ -18478,13 +18478,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="132" t="n">
-        <v>4.034208977549759</v>
+        <v>4.034208977549761</v>
       </c>
       <c r="V72" s="130" t="n">
         <v>3.004310589767974</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891315731220903</v>
+        <v>0.9891315731220905</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -18652,10 +18652,10 @@
         <v>428</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7725.40912219813</v>
+        <v>7725.409122198131</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2374.418161174764</v>
+        <v>2374.418161174763</v>
       </c>
       <c r="L75" s="131" t="n">
         <v>535.5877718652724</v>
@@ -18667,34 +18667,34 @@
         <v>10635.41505523817</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8643.557255466281</v>
+        <v>8643.557255466285</v>
       </c>
       <c r="Q75" s="131" t="n">
         <v>2736.307259689338</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>615.2216261623436</v>
+        <v>615.2216261623435</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T75" s="132" t="n">
-        <v>11995.08614131796</v>
+        <v>11995.08614131797</v>
       </c>
       <c r="V75" s="130" t="n">
         <v>9438.884141585029</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3047.279734764492</v>
+        <v>3047.279734764493</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>680.2887679058531</v>
+        <v>680.2887679058533</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z75" s="132" t="n">
-        <v>13166.45264425537</v>
+        <v>13166.45264425538</v>
       </c>
     </row>
     <row r="76">
@@ -19054,49 +19054,49 @@
         <v>2509</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="L81" s="131" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M81" s="131" t="n">
         <v>2908.033523731806</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2908.033523731808</v>
+        <v>2908.033523731807</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>-3.637978807091713e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="S81" s="131" t="n">
         <v>3233.974567580811</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>3233.974567580811</v>
+        <v>3233.974567580808</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>3567.196203083912</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>3567.196203083913</v>
+        <v>3567.19620308391</v>
       </c>
     </row>
     <row r="82">
@@ -19399,7 +19399,7 @@
         <v>3507.389747664738</v>
       </c>
       <c r="L86" s="143" t="n">
-        <v>892.609157537412</v>
+        <v>892.6091575374119</v>
       </c>
       <c r="M86" s="143" t="n">
         <v>2908.033523731806</v>
@@ -19592,10 +19592,10 @@
         <v>12611.11616612652</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>4233.290510417969</v>
+        <v>4233.290510417968</v>
       </c>
       <c r="L89" s="128" t="n">
-        <v>1147.809136917205</v>
+        <v>1147.809136917204</v>
       </c>
       <c r="M89" s="128" t="n">
         <v>0</v>
@@ -19604,7 +19604,7 @@
         <v>17992.21581346169</v>
       </c>
       <c r="P89" s="127" t="n">
-        <v>12526.95646477333</v>
+        <v>12526.95646477334</v>
       </c>
       <c r="Q89" s="128" t="n">
         <v>4162.671517703222</v>
@@ -19616,7 +19616,7 @@
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>17813.43158786618</v>
+        <v>17813.43158786619</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>12438.45133966805</v>
@@ -19656,19 +19656,19 @@
         <v>21130</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>14504.79819544821</v>
+        <v>14504.7981954482</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.477550993601</v>
+        <v>7846.477550993602</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>2325.731440101695</v>
+        <v>2325.731440101696</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>24677.00718654351</v>
+        <v>24677.0071865435</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>15891.30418643938</v>
@@ -19683,7 +19683,7 @@
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>27000.84940712616</v>
+        <v>27000.84940712615</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>17731.73815568648</v>
@@ -19729,7 +19729,7 @@
         <v>891.9942898548878</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
@@ -19741,10 +19741,10 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.639414952088</v>
+        <v>890.6394149520879</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
@@ -19759,7 +19759,7 @@
         <v>887.5202998056624</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -19863,7 +19863,7 @@
         <v>3581.617170974006</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>982.7439641763199</v>
+        <v>982.7439641763198</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -20262,7 +20262,7 @@
         <v>5637.393210158669</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1656.13541467506</v>
+        <v>1656.135414675056</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>607.4898571432232</v>
@@ -20289,19 +20289,19 @@
         <v>35937.12677084539</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>6144.224276925175</v>
+        <v>6144.224276925161</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1767.142052340063</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>655.1214664631962</v>
+        <v>655.1214664631952</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>30693.9708717485</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>39260.45866747694</v>
+        <v>39260.45866747692</v>
       </c>
     </row>
     <row r="100">
@@ -20601,7 +20601,7 @@
         <v>67280.10770430029</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>18233.5953625737</v>
+        <v>18233.59536257369</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>5121.900829719571</v>
@@ -20628,13 +20628,13 @@
         <v>149710.839179817</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>72515.58812458278</v>
+        <v>72515.58812458276</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>20155.89452033806</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>6089.177142089051</v>
+        <v>6089.17714208905</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>30693.9708717485</v>
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>55708663.09676259</v>
+        <v>55708663.09676257</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>68660.92484379245</v>
+        <v>68660.92484379247</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>6215534.477519744</v>
+        <v>6215534.477519743</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>0</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>3649660.287984258</v>
+        <v>3649660.287984257</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>0</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>3041768.766676024</v>
+        <v>3041768.766676023</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>0</v>
@@ -22423,10 +22423,10 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>2006758.971569033</v>
+        <v>2006758.971569034</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>3570.123843302602</v>
+        <v>3570.123843302601</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1209246.390037417</v>
+        <v>1209246.390037416</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>1182.728456312894</v>
@@ -22864,7 +22864,7 @@
         <v>1022634.165864078</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>929.2709615946428</v>
+        <v>929.2709615946427</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -23449,7 +23449,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>9810448.624385368</v>
+        <v>9810448.624385366</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>0</v>
@@ -23477,13 +23477,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.0648471281</v>
+        <v>6320.064847128099</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.407495872959</v>
+        <v>3125.407495872958</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7877512450654</v>
+        <v>790.7877512450652</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -23492,28 +23492,28 @@
         <v>10236.26009424612</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.830358097972</v>
+        <v>6124.830358097973</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>3021.838043207604</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.91190356957</v>
+        <v>757.9119035695702</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>9904.580304875144</v>
+        <v>9904.580304875146</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.504189498098</v>
+        <v>5957.504189498099</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>2933.086637895056</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.230904643476</v>
+        <v>729.2309046434758</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -23533,7 +23533,7 @@
         <v>4168985.67548562</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>5238.026133777927</v>
+        <v>5238.026133777928</v>
       </c>
     </row>
     <row r="54">
@@ -23558,13 +23558,13 @@
         <v>21126</v>
       </c>
       <c r="J54" s="130" t="n">
-        <v>14501.73838215771</v>
+        <v>14501.7383821577</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.46940470681</v>
+        <v>7845.469404706811</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>2325.731440101695</v>
+        <v>2325.731440101696</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
@@ -23645,7 +23645,7 @@
         <v>891.9942898548878</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
@@ -23657,10 +23657,10 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.639414952088</v>
+        <v>890.6394149520879</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
@@ -23675,7 +23675,7 @@
         <v>887.5202998056624</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>3177826.490204261</v>
+        <v>3177826.49020426</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>656.4516549924249</v>
@@ -23807,31 +23807,31 @@
         <v>1207.199009799243</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>447.1561923110474</v>
+        <v>447.1561923110473</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8263.713017195194</v>
+        <v>8263.713017195192</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6533.070130571056</v>
+        <v>6533.070130571055</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1132.596079860724</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>428.0039475295338</v>
+        <v>428.0039475295337</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8093.670157961314</v>
+        <v>8093.670157961312</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6654.18468522172</v>
+        <v>6654.184685221721</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1147.293027687765</v>
@@ -23938,7 +23938,7 @@
         <v>896423.6340824055</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>542.4553145801295</v>
+        <v>542.4553145801294</v>
       </c>
     </row>
     <row r="59">
@@ -24287,34 +24287,34 @@
         <v>22805</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5637.393210158669</v>
+        <v>5637.393210158662</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1656.135414675062</v>
+        <v>1656.135414675058</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>607.4898571432227</v>
+        <v>607.4898571432223</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>22204.72312108167</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>30105.74160305862</v>
+        <v>30105.74160305861</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5875.167457966767</v>
+        <v>5875.167457966774</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1703.952920346313</v>
+        <v>1703.952920346315</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>629.784487875077</v>
+        <v>629.7844878750766</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>24494.24733707641</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32703.15220326457</v>
+        <v>32703.15220326458</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>6144.224276925168</v>
@@ -24592,7 +24592,7 @@
         <v>245617.9934694493</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>71.41468242441329</v>
+        <v>71.41468242441327</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -24673,7 +24673,7 @@
         <v>213914.9009928257</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>416.2752595267629</v>
+        <v>416.275259526763</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -24698,7 +24698,7 @@
         <v>109542</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>53083.94013616577</v>
+        <v>53083.94013616576</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>14726.20561490896</v>
@@ -24734,7 +24734,7 @@
         <v>15913.04608529102</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>5035.70598772958</v>
+        <v>5035.705987729579</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>27126.77466866459</v>
@@ -24908,22 +24908,22 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6291.051318998416</v>
+        <v>6291.051318998417</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1107.88301454501</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.0213856721393</v>
+        <v>357.0213856721392</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7755.955719215565</v>
+        <v>7755.955719215566</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6402.126106675359</v>
+        <v>6402.126106675362</v>
       </c>
       <c r="Q71" s="128" t="n">
         <v>1140.833474495618</v>
@@ -24935,22 +24935,22 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7908.851282991038</v>
+        <v>7908.851282991041</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6480.947150169953</v>
+        <v>6480.947150169954</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.110724660194</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>373.1823864536181</v>
+        <v>373.1823864536182</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8025.240261283765</v>
+        <v>8025.240261283766</v>
       </c>
     </row>
     <row r="72">
@@ -24990,7 +24990,7 @@
         <v>4.06795957729254</v>
       </c>
       <c r="P72" s="130" t="n">
-        <v>3.034850177968129</v>
+        <v>3.034850177968131</v>
       </c>
       <c r="Q72" s="131" t="n">
         <v>0.99935879958163</v>
@@ -25002,13 +25002,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="132" t="n">
-        <v>4.034208977549759</v>
+        <v>4.034208977549761</v>
       </c>
       <c r="V72" s="130" t="n">
         <v>3.004310589767974</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891315731220903</v>
+        <v>0.9891315731220905</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -25176,10 +25176,10 @@
         <v>428</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7725.40912219813</v>
+        <v>7725.409122198131</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2374.418161174764</v>
+        <v>2374.418161174763</v>
       </c>
       <c r="L75" s="131" t="n">
         <v>535.5877718652724</v>
@@ -25191,34 +25191,34 @@
         <v>10635.41505523817</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8643.557255466281</v>
+        <v>8643.557255466285</v>
       </c>
       <c r="Q75" s="131" t="n">
         <v>2736.307259689338</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>615.2216261623436</v>
+        <v>615.2216261623435</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T75" s="132" t="n">
-        <v>11995.08614131796</v>
+        <v>11995.08614131797</v>
       </c>
       <c r="V75" s="130" t="n">
         <v>9438.884141585029</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3047.279734764492</v>
+        <v>3047.279734764493</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>680.2887679058531</v>
+        <v>680.2887679058533</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z75" s="132" t="n">
-        <v>13166.45264425537</v>
+        <v>13166.45264425538</v>
       </c>
     </row>
     <row r="76">
@@ -25578,49 +25578,49 @@
         <v>2509</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="L81" s="131" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M81" s="131" t="n">
         <v>2908.033523731806</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2908.033523731808</v>
+        <v>2908.033523731807</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>-3.637978807091713e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="S81" s="131" t="n">
         <v>3233.974567580811</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>3233.974567580811</v>
+        <v>3233.974567580808</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>3567.196203083912</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>3567.196203083913</v>
+        <v>3567.19620308391</v>
       </c>
     </row>
     <row r="82">
@@ -25923,7 +25923,7 @@
         <v>3507.389747664738</v>
       </c>
       <c r="L86" s="143" t="n">
-        <v>892.609157537412</v>
+        <v>892.6091575374119</v>
       </c>
       <c r="M86" s="143" t="n">
         <v>2908.033523731806</v>
@@ -26116,10 +26116,10 @@
         <v>12611.11616612652</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>4233.290510417969</v>
+        <v>4233.290510417968</v>
       </c>
       <c r="L89" s="128" t="n">
-        <v>1147.809136917205</v>
+        <v>1147.809136917204</v>
       </c>
       <c r="M89" s="128" t="n">
         <v>0</v>
@@ -26128,7 +26128,7 @@
         <v>17992.21581346169</v>
       </c>
       <c r="P89" s="127" t="n">
-        <v>12526.95646477333</v>
+        <v>12526.95646477334</v>
       </c>
       <c r="Q89" s="128" t="n">
         <v>4162.671517703222</v>
@@ -26140,7 +26140,7 @@
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>17813.43158786618</v>
+        <v>17813.43158786619</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>12438.45133966805</v>
@@ -26180,19 +26180,19 @@
         <v>21130</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>14504.79819544821</v>
+        <v>14504.7981954482</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.477550993601</v>
+        <v>7846.477550993602</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>2325.731440101695</v>
+        <v>2325.731440101696</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>24677.00718654351</v>
+        <v>24677.0071865435</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>15891.30418643938</v>
@@ -26207,7 +26207,7 @@
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>27000.84940712616</v>
+        <v>27000.84940712615</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>17731.73815568648</v>
@@ -26253,7 +26253,7 @@
         <v>891.9942898548878</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
@@ -26265,10 +26265,10 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.639414952088</v>
+        <v>890.6394149520879</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
@@ -26283,7 +26283,7 @@
         <v>887.5202998056624</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -26387,7 +26387,7 @@
         <v>3581.617170974006</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>982.7439641763199</v>
+        <v>982.7439641763198</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -26786,7 +26786,7 @@
         <v>5637.393210158669</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1656.13541467506</v>
+        <v>1656.135414675056</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>607.4898571432232</v>
@@ -26813,19 +26813,19 @@
         <v>35937.12677084539</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>6144.224276925175</v>
+        <v>6144.224276925161</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1767.142052340063</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>655.1214664631962</v>
+        <v>655.1214664631952</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>30693.9708717485</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>39260.45866747694</v>
+        <v>39260.45866747692</v>
       </c>
     </row>
     <row r="100">
@@ -27125,7 +27125,7 @@
         <v>67280.10770430029</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>18233.5953625737</v>
+        <v>18233.59536257369</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>5121.900829719571</v>
@@ -27152,13 +27152,13 @@
         <v>149710.839179817</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>72515.58812458278</v>
+        <v>72515.58812458276</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>20155.89452033806</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>6089.177142089051</v>
+        <v>6089.17714208905</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>30693.9708717485</v>
@@ -28200,7 +28200,7 @@
         <v>69272530.81205237</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.1061648711</v>
+        <v>82393.10616487112</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>17407719.14889541</v>
+        <v>17407719.1488954</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>19791.41132971137</v>
@@ -28351,7 +28351,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>11231931.67480008</v>
+        <v>11231931.67480009</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>12591.15395972414</v>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>6672923.775079137</v>
+        <v>6672923.775079138</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>0</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>3344521.812389606</v>
+        <v>3344521.812389607</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>2764.898270390802</v>
@@ -29027,7 +29027,7 @@
         <v>1704248.498563595</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>1964.648020269052</v>
+        <v>1964.648020269053</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -29181,7 +29181,7 @@
         <v>1435810.873131995</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>2609.805879037139</v>
+        <v>2609.80587903714</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -30001,13 +30001,13 @@
         <v>11283</v>
       </c>
       <c r="J53" s="127" t="n">
-        <v>6320.0648471281</v>
+        <v>6320.064847128099</v>
       </c>
       <c r="K53" s="128" t="n">
-        <v>3125.407495872959</v>
+        <v>3125.407495872958</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>790.7877512450654</v>
+        <v>790.7877512450652</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -30016,28 +30016,28 @@
         <v>10236.26009424612</v>
       </c>
       <c r="P53" s="127" t="n">
-        <v>6124.830358097972</v>
+        <v>6124.830358097973</v>
       </c>
       <c r="Q53" s="128" t="n">
         <v>3021.838043207604</v>
       </c>
       <c r="R53" s="128" t="n">
-        <v>757.91190356957</v>
+        <v>757.9119035695702</v>
       </c>
       <c r="S53" s="128" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="129" t="n">
-        <v>9904.580304875144</v>
+        <v>9904.580304875146</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>5957.504189498098</v>
+        <v>5957.504189498099</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>2933.086637895056</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>729.230904643476</v>
+        <v>729.2309046434758</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -30082,13 +30082,13 @@
         <v>21126</v>
       </c>
       <c r="J54" s="130" t="n">
-        <v>14501.73838215771</v>
+        <v>14501.7383821577</v>
       </c>
       <c r="K54" s="131" t="n">
-        <v>7845.46940470681</v>
+        <v>7845.469404706811</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>2325.731440101695</v>
+        <v>2325.731440101696</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
@@ -30169,7 +30169,7 @@
         <v>891.9942898548878</v>
       </c>
       <c r="L55" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M55" s="131" t="n">
         <v>0</v>
@@ -30181,10 +30181,10 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>890.639414952088</v>
+        <v>890.6394149520879</v>
       </c>
       <c r="R55" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S55" s="131" t="n">
         <v>0</v>
@@ -30199,7 +30199,7 @@
         <v>887.5202998056624</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -30297,7 +30297,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>1648202.438743795</v>
+        <v>1648202.438743794</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>4278.468882048729</v>
@@ -30331,31 +30331,31 @@
         <v>1207.199009799243</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>447.1561923110474</v>
+        <v>447.1561923110473</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8263.713017195194</v>
+        <v>8263.713017195192</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6533.070130571056</v>
+        <v>6533.070130571055</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1132.596079860724</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>428.0039475295338</v>
+        <v>428.0039475295337</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8093.670157961314</v>
+        <v>8093.670157961312</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>6654.18468522172</v>
+        <v>6654.184685221721</v>
       </c>
       <c r="W57" s="131" t="n">
         <v>1147.293027687765</v>
@@ -30811,34 +30811,34 @@
         <v>22805</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>5637.393210158669</v>
+        <v>5637.393210158662</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>1656.135414675062</v>
+        <v>1656.135414675058</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>607.4898571432227</v>
+        <v>607.4898571432223</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>22204.72312108167</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>30105.74160305862</v>
+        <v>30105.74160305861</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>5875.167457966767</v>
+        <v>5875.167457966774</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>1703.952920346313</v>
+        <v>1703.952920346315</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>629.784487875077</v>
+        <v>629.7844878750766</v>
       </c>
       <c r="S63" s="131" t="n">
         <v>24494.24733707641</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>32703.15220326457</v>
+        <v>32703.15220326458</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>6144.224276925168</v>
@@ -31222,7 +31222,7 @@
         <v>109542</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>53083.94013616577</v>
+        <v>53083.94013616576</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>14726.20561490896</v>
@@ -31258,7 +31258,7 @@
         <v>15913.04608529102</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>5035.70598772958</v>
+        <v>5035.705987729579</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>27126.77466866459</v>
@@ -31432,22 +31432,22 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6291.051318998416</v>
+        <v>6291.051318998417</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1107.88301454501</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>357.0213856721393</v>
+        <v>357.0213856721392</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7755.955719215565</v>
+        <v>7755.955719215566</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6402.126106675359</v>
+        <v>6402.126106675362</v>
       </c>
       <c r="Q71" s="128" t="n">
         <v>1140.833474495618</v>
@@ -31459,22 +31459,22 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7908.851282991038</v>
+        <v>7908.851282991041</v>
       </c>
       <c r="V71" s="127" t="n">
-        <v>6480.947150169953</v>
+        <v>6480.947150169954</v>
       </c>
       <c r="W71" s="128" t="n">
         <v>1171.110724660194</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>373.1823864536181</v>
+        <v>373.1823864536182</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="Z71" s="129" t="n">
-        <v>8025.240261283765</v>
+        <v>8025.240261283766</v>
       </c>
     </row>
     <row r="72">
@@ -31514,7 +31514,7 @@
         <v>4.06795957729254</v>
       </c>
       <c r="P72" s="130" t="n">
-        <v>3.034850177968129</v>
+        <v>3.034850177968131</v>
       </c>
       <c r="Q72" s="131" t="n">
         <v>0.99935879958163</v>
@@ -31526,13 +31526,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="132" t="n">
-        <v>4.034208977549759</v>
+        <v>4.034208977549761</v>
       </c>
       <c r="V72" s="130" t="n">
         <v>3.004310589767974</v>
       </c>
       <c r="W72" s="131" t="n">
-        <v>0.9891315731220903</v>
+        <v>0.9891315731220905</v>
       </c>
       <c r="X72" s="131" t="n">
         <v>0</v>
@@ -31700,10 +31700,10 @@
         <v>428</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7725.40912219813</v>
+        <v>7725.409122198131</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2374.418161174764</v>
+        <v>2374.418161174763</v>
       </c>
       <c r="L75" s="131" t="n">
         <v>535.5877718652724</v>
@@ -31715,34 +31715,34 @@
         <v>10635.41505523817</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8643.557255466281</v>
+        <v>8643.557255466285</v>
       </c>
       <c r="Q75" s="131" t="n">
         <v>2736.307259689338</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>615.2216261623436</v>
+        <v>615.2216261623435</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T75" s="132" t="n">
-        <v>11995.08614131796</v>
+        <v>11995.08614131797</v>
       </c>
       <c r="V75" s="130" t="n">
         <v>9438.884141585029</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3047.279734764492</v>
+        <v>3047.279734764493</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>680.2887679058531</v>
+        <v>680.2887679058533</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z75" s="132" t="n">
-        <v>13166.45264425537</v>
+        <v>13166.45264425538</v>
       </c>
     </row>
     <row r="76">
@@ -32102,49 +32102,49 @@
         <v>2509</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="L81" s="131" t="n">
-        <v>3.410605131648481e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="M81" s="131" t="n">
         <v>2908.033523731806</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>2908.033523731808</v>
+        <v>2908.033523731807</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>0</v>
+        <v>-3.637978807091713e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
         <v>4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="S81" s="131" t="n">
         <v>3233.974567580811</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>3233.974567580811</v>
+        <v>3233.974567580808</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>3567.196203083912</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>3567.196203083913</v>
+        <v>3567.19620308391</v>
       </c>
     </row>
     <row r="82">
@@ -32447,7 +32447,7 @@
         <v>3507.389747664738</v>
       </c>
       <c r="L86" s="143" t="n">
-        <v>892.609157537412</v>
+        <v>892.6091575374119</v>
       </c>
       <c r="M86" s="143" t="n">
         <v>2908.033523731806</v>
@@ -32640,10 +32640,10 @@
         <v>12611.11616612652</v>
       </c>
       <c r="K89" s="128" t="n">
-        <v>4233.290510417969</v>
+        <v>4233.290510417968</v>
       </c>
       <c r="L89" s="128" t="n">
-        <v>1147.809136917205</v>
+        <v>1147.809136917204</v>
       </c>
       <c r="M89" s="128" t="n">
         <v>0</v>
@@ -32652,7 +32652,7 @@
         <v>17992.21581346169</v>
       </c>
       <c r="P89" s="127" t="n">
-        <v>12526.95646477333</v>
+        <v>12526.95646477334</v>
       </c>
       <c r="Q89" s="128" t="n">
         <v>4162.671517703222</v>
@@ -32664,7 +32664,7 @@
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>17813.43158786618</v>
+        <v>17813.43158786619</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>12438.45133966805</v>
@@ -32704,19 +32704,19 @@
         <v>21130</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>14504.79819544821</v>
+        <v>14504.7981954482</v>
       </c>
       <c r="K90" s="131" t="n">
-        <v>7846.477550993601</v>
+        <v>7846.477550993602</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>2325.731440101695</v>
+        <v>2325.731440101696</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>24677.00718654351</v>
+        <v>24677.0071865435</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>15891.30418643938</v>
@@ -32731,7 +32731,7 @@
         <v>0</v>
       </c>
       <c r="T90" s="132" t="n">
-        <v>27000.84940712616</v>
+        <v>27000.84940712615</v>
       </c>
       <c r="V90" s="130" t="n">
         <v>17731.73815568648</v>
@@ -32777,7 +32777,7 @@
         <v>891.9942898548878</v>
       </c>
       <c r="L91" s="131" t="n">
-        <v>58.12643138112766</v>
+        <v>58.12643138112765</v>
       </c>
       <c r="M91" s="131" t="n">
         <v>0</v>
@@ -32789,10 +32789,10 @@
         <v>19985.32270203581</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>890.639414952088</v>
+        <v>890.6394149520879</v>
       </c>
       <c r="R91" s="131" t="n">
-        <v>58.03372169181661</v>
+        <v>58.0337216918166</v>
       </c>
       <c r="S91" s="131" t="n">
         <v>0</v>
@@ -32807,7 +32807,7 @@
         <v>887.5202998056624</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>57.82394798115031</v>
+        <v>57.82394798115032</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -32911,7 +32911,7 @@
         <v>3581.617170974006</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>982.7439641763199</v>
+        <v>982.7439641763198</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>0</v>
@@ -33310,7 +33310,7 @@
         <v>5637.393210158669</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>1656.13541467506</v>
+        <v>1656.135414675056</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>607.4898571432232</v>
@@ -33337,19 +33337,19 @@
         <v>35937.12677084539</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>6144.224276925175</v>
+        <v>6144.224276925161</v>
       </c>
       <c r="W99" s="131" t="n">
         <v>1767.142052340063</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>655.1214664631962</v>
+        <v>655.1214664631952</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>30693.9708717485</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>39260.45866747694</v>
+        <v>39260.45866747692</v>
       </c>
     </row>
     <row r="100">
@@ -33649,7 +33649,7 @@
         <v>67280.10770430029</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>18233.5953625737</v>
+        <v>18233.59536257369</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>5121.900829719571</v>
@@ -33676,13 +33676,13 @@
         <v>149710.839179817</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>72515.58812458278</v>
+        <v>72515.58812458276</v>
       </c>
       <c r="W104" s="143" t="n">
         <v>20155.89452033806</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>6089.177142089051</v>
+        <v>6089.17714208905</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>30693.9708717485</v>
